--- a/data/medicina/asistencia/asistencia_medicina.xlsx
+++ b/data/medicina/asistencia/asistencia_medicina.xlsx
@@ -8,23 +8,23 @@
   </bookViews>
   <sheets>
     <sheet name="AR_Sección 1_Seminario" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="JCS_Sección 1_Seminario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TY_Sección 1_Seminario" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="XX_Sección 1_Seminario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="EG_Sección 1_Seminario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="JCS_Sección 1_Seminario" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TY_Sección 1_Seminario" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="AR_Sección 2_Seminario" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="JCS_Sección 2_Seminario" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TY_Sección 2_Seminario" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="XX_Sección 2_Seminario" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="EG_Sección 2_Seminario" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="JCS_Sección 2_Seminario" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TY_Sección 2_Seminario" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'AR_Sección 1_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'JCS_Sección 1_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'TY_Sección 1_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'XX_Sección 1_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'EG_Sección 1_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'JCS_Sección 1_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'TY_Sección 1_Seminario'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'AR_Sección 2_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'JCS_Sección 2_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'TY_Sección 2_Seminario'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'XX_Sección 2_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'EG_Sección 2_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'JCS_Sección 2_Seminario'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'TY_Sección 2_Seminario'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Riquelme Herrera, Alexander Nathan</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -719,6 +719,696 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Araya Buscovich, Benjamín Kamilo</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Araya Derpich, Camila Paz</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Auil Loma-Osorio, Ananda Paz</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Becerra Barrios, Joan Ignacio</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Calderón Tapia, Christopher Carlos</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Chesney Alonso, María José</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Díaz Donoso, Sergio Eduardo</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Díaz Oyarzún, Vicente Eduardo</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Dinamarca Ramírez, Anaís Catalina</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Ferrada Hidalgo, Santiago Antonio</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Giliberto Lara, Jose Ignacio</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Grollmus Chávez, Agatha Kertin Schmetterling</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Gutiérrez Monsalve, Magdalena Sofía Haydée</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Hewitt Castillo, Stephani Laura</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hojas Widmer, María Rosario</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Jorquera Peña, Benjamín Rafael</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Manríquez Astete, Antonia Belén</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Martínez Peiret, Tomás Lautaro</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Meléndez Godoy, Catalina Teresa</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Meléndez Muñoz, Laura Annahis</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Molina Osorio, Tamara Andrea</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Mora Aravena, Vicente Ignacio</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Neira Orellana, Cristián Alejandro</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Ortega Rodríguez, Eduardo Antonio</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Pinto Millán, Catalina Haydée</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Ramírez Tapia, Ignacio Benjamín</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Rivas Poblete, Valentina Paz</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Ulloa Silva, Benjamín Jesús</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Vargas Miranda, Gonzalo Andrés</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Vidal Barría, Magdalena Alicia de los Angeles</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -731,7 +1421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -756,7 +1446,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: JCS</t>
+          <t>Profesor: EG</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -951,7 +1641,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Guerra López, Eduardo Andrés</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -971,6 +1661,696 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Achurra Cortés, Leonor</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Aramayo León, Oscar Ivan</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Arce Contreras, Magdalena Francisca</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Arias Jara, Marthina Antonella</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Baumann Figueroa, Selva Ayelén</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Canales Aravena, Constanza Andrea</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cid Gamboa, Lisa Araceli</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Díaz Cortés, Valentina Paz</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Dorr Vial, Juan Carlos</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Fernández Meneses, Rayen Alejandra</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Fredes Rebolledo, Vanina Andrea</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>González Ravanal, José Tomás</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>González Valenzuela, Gabriela Amanda</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Gutiérrez Angulo, Isidora Antonia</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Gutiérrez Solís, Sebastian Andrés</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Huerta Monsalve, Alonso Cristobal</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Inostroza Pineda, Alexia Isabel</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Marín Salazar, Fernanda</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Meza Astete, Agustín Antonio</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Naranjo Angel, Sofía Belén</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Oyarce Gallardo, Katherine Fernanda</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Pizarro Orrego, Manuel Alberto</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Román Gutiérrez, Sofía Antonia</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Salas González, Sebastián Ignacio</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Salvo Martínez, Martín Amaro</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Tapia Díaz, Catalina Andrea</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Toro Flores, Cristóbal Javier</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Valenzuela Walker, Andrea Carolina</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Zabala Huanchicay, Diego Alonso</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Zambón Jerez, Josefa Belén</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -983,7 +2363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1008,7 +2388,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: TY</t>
+          <t>Profesor: JCS</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1203,7 +2583,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Salas Galaz, Juan Carlos</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -1223,6 +2603,696 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Arévalo Quiñones, Lucas Maximiliano</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Carrasco Flores, Alonso Joaquín</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Castillo Dintrans, Marco Andrés</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>García Farías, Benjamín Alejandro</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Garrido Sepúlveda, Simón Patricio</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>González Lobos, Millaray Antonia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Letson, Bailey Frances</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Lorca Godoy, Ignacio Andrés</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Marambio Pinto, Ignacia Valentina</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Maturana Ramírez, Rocío Mariel</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Montenegro Ramírez, Ignacio Manuel</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Morales Díaz, José Ignacio</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Morán González, Matías Alonso</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Norambuena Garcés, Martín Lincoln</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Ortiz Hernández, Gaspar Eduardo</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Osorio Taco, Kiara Rosa</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Pino Miranda, Laura Carolina</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Pozo Gortari, Martina Montserrat</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Quiroga Poblete, Antonella Ignacia</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Restovic Ceballos, Cristóbal Felipe</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Reveco Espinoza, Juan Ignacio</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Reyes Rosales, Abigail Antonia</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Rodríguez Montesinos, Matías Ignacio</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Santibáñez Zapata, Agustina Isabel</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Silva Berríos, Gaspar Alonso</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Soto Álvarez, Santiago Alonso</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Uribe Baeza, Sebastián Andrés</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Carrión, Gustavo Javier</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Vicuña López, Antonio</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Zapata Gonzalez, Claudia Valentina</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1235,7 +3305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1260,7 +3330,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: XX</t>
+          <t>Profesor: TY</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1455,7 +3525,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -1475,6 +3545,696 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Albornoz Sepúlveda, Martin Renato</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Barrera González, Anezka Javiera</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Barría Gallardo, Catalina Paz</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Chacc Garrido, Gabriela Ignacia</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Contreras González, Bernardo Alonso</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Flores Delard de Rigoulieres, Martina Isidora</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Fuentes Casanueva, Santiago Andrés</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>González Cisternas, María Ignacia Belén</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>González Oviedo, Josefa Ignacia</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Gonzalez Torres, Antonia Belen</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Gutiérrez Moreno, Emilio Marcelo</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Iglesias Clark, Maria Ignacia</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Lundgren Torres, Niklas Andreas</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Muñoz Escobar, Aurora</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Olazo Ponce, Isabel Josefa</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Olivares Pinto, Sofia Carolina</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Ortega Olivares, Clara</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Osses Ibarra, Laura Rayen</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Peña Cifuentes, Camila Alejandra</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Pérez Morales, Amalia Carolina</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Pino Cerda, Alonso Thomas</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Rivas Padilla, Smilian Patricio</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Salazar Palma, Gonzalo Fermín</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Sandoval Escudero, Trinidad María</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Soto Torres, Maríajesús</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Suazo Marín, José Ignacio</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Torres Cisternas, José Ignacio</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Ulriksen Palma, Nicolás Federico</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Valderrama Armijo, Lucas Facundo</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Vargas Marticorena, Camila Javiera</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1487,7 +4247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1707,7 +4467,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -1727,6 +4487,719 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Riquelme Herrera, Alexander Nathan</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Abarca Ibeas, Gionardy Alejandro</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Ahumada Del Canto, José Cristóbal</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Arancibia Aguirre, Constanza Adriana</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Baez Carvajal, Cristóbal Gabriel</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Barbatto Romero, Benjamín Eduardo</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Barrera Soto, Cristhian Diego</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Blanco Cea, Antonia Fernanda</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Caamaño Pino, Marco Antonio</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Canitrot Proschle, Diego</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Canobra Andrade, Esperanza Rayen</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Castañeda Madrid, Francisco Javier</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Cerda Céspedes, Julián Ignacio</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Cornejo Barrera, Ramiro Andrés</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Escudero Yáñez, Tomás Martín</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>González Hernández, Diego Antonio</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Hidalgo Vergara, Beatriz de la Luz</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Ibáñez García, Sebastián Alonso</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Mamani Choque, Danilo José</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Marchant Anwandter, Francoise Nataly</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Nash Lynch, Emily Camille</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Navarrete Ureta, Vicente Antonio</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Pinochet Ferretti, Gonzalo Andrés</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Pinto Voigt, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Rapu Jara, Alejandra Lucía</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Tapia Boksamy, Amanda</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Valentin Sepúlveda, Gustavo Ignacio</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Valenzuela Jofré, Sofía Isidora</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Vargas Rojas, Pablo Andrés</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Veas Morgado, Victoria Helena</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1739,7 +5212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1764,7 +5237,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: JCS</t>
+          <t>Profesor: EG</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1959,7 +5432,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -1979,6 +5452,696 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Guerra López, Eduardo Andrés</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Ampuero Ascencio, Antonia Paz</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Araya Muñoz, Krishna Eylin Paz</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Castillo Alfaro, Pia Ignacia</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Castro Moya, Cecilia Isabel</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Duque Valenzuela, María Constanza</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Flores Morote, Alexandra Natalì</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>González Jiménez, Felipe Agustin</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Klingenberg Massanes, Maximiliano</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Olivares Prieto, Thomas Alexander</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Ortiz Guzmán, Catalina Paz</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Ortiz Mariángel, Monserrat Lourdes del Carmen</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Pedreros Saumont, Javier Alonso</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Pérez Leiva, Isidora Antonia</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Pérez Rodríguez, Diego Alejandro</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Pérez Román, Camila Andrea</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Pertuze Dufraix, Ignacio Javier</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Polanco Ríos, Laura Paz</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Quintana Cerda, María Francisca Esperanza</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Roa Leyton, Francisca Belén</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Rodríguez Sandoval, Renato Alejandro</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Salinas Arriagada, Fernando Alonso</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Sánchez Leiva, Fabián Andrés</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Ugarte Parra, Francisca Antonia</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Urra Torrejón, Catalina Ignacia</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Veas Araya, Juan Pablo</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Verdugo González, Isidora Jesús</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Vergara Núñez, Martina Belén</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Villegas Cuevas, Sebastian Alejandro</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1991,7 +6154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2016,7 +6179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: TY</t>
+          <t>Profesor: JCS</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2211,7 +6374,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -2231,6 +6394,696 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Salas Galaz, Juan Carlos</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Arancibia González, Vicente Isaías</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Armijo Madrid, Sofia Belén</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Becerra Barría, Josefa Monserrat</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Benavides Soto, Martín Antonio</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Berbelagua Montenegro, Micaela Beatriz</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Berríos Oyarzún, Antonia Elena</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Bórquez Seguel, Santiago Nicolás</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Bossi González, Lucas Ignacio</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Bravo Escalona, Matilda Sofía</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Callejas Acevedo, José Manuel</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Carrión Soto, Laura Trinidad</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Enei Gjurovic, Laura Florencia</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Fuentes López, Alessandro Javier</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Fuenzalida Marambio, Sofía Beatriz</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Gálvez Almonacid, Valentina Domenica</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Gómez Pardo, Dimitri</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Higuera Cerda, Genesis Belen</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Lizana Patterson, Renata Paz</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Madrid Serrano, Vicente Alonso</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Mejías Ortega, Josefa Paz</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Moraga Garrido, Benjamín Antonio</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Moraga González, Martina Paz</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Paredes Panozo, Valentina Tamara</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Reimán Aracena, Rayen</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>San Martín Orellana, Sofía Ignacia</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Seguel Muñoz, Josefa Isidora</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Ulate Mosqueira, Josefa Paz</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Veloso Rodríguez, Benjamín Ignacio</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2243,7 +7096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2268,7 +7121,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesor: XX</t>
+          <t>Profesor: TY</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2463,7 +7316,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(Pegar aquí lista de estudiantes)</t>
+          <t>Galaz Paredes, Ingrid Del Pilar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -2483,6 +7336,696 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Yáñez Cáceres, Joriv Tomás Vicente</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Acevedo Álvarez, Martin Alonso</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Bianchi Prieto, José Agustín</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Celis Toncio, Benjamín Antonio</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Chibbaro Cifuentes, Isabella Fabiola</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Ciuffardi Thedy, Martina Belén</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cohen Morales, Antonia Cecilia</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Cohen Morales, Javiera Cecilia</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Contreras Barraza, Sofía Loreto</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Delgado Díaz, Génesis Belén</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Del Real Linares, Aurora Josefa</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Gallardo Cobian, Cristóbal Alonso</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>González Rodríguez, Macarena Ignacia</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Guzmán Lorca, Sofía Antonia</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Korn Gajardo, Catalina Ignacia</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Lagos Yáñez, Martín Alejandro</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Leiva Méndez, María Francisca</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Martínez Cerda, René Ernesto</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Martínez Figueroa, Fernanda Grace</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Moya Aguero, Lola Galatea</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Navarro Benítez, Juan Ignacio</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Peña González, Mateo Alfonso</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Ponce Toro, Rocío Catalina</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Quiroz Castro, Felipe Octavio</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Ramos Rojas, Carlos Matías Domingo</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Sanchez Torres, Juan Diego</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Troncoso Putney, Daniela Anahí</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Valdebenito Sierra, Tihare Yenira</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Valenzuela Acevedo, Sofía Carolina</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Yunis Diez, Magdalena María</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
